--- a/artfynd/A 45884-2021 artfynd.xlsx
+++ b/artfynd/A 45884-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45884-2021 artfynd.xlsx
+++ b/artfynd/A 45884-2021 artfynd.xlsx
@@ -1716,7 +1716,7 @@
         <v>133625236</v>
       </c>
       <c r="B11" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>133625237</v>
       </c>
       <c r="B12" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45884-2021 artfynd.xlsx
+++ b/artfynd/A 45884-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95887257</v>
+        <v>95886455</v>
       </c>
       <c r="B2" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571813.8594684753</v>
+        <v>571761</v>
       </c>
       <c r="R2" t="n">
-        <v>6701525.235171015</v>
+        <v>6701589</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,7 +747,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,7 +757,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,12 +787,7 @@
         <v>95886494</v>
       </c>
       <c r="B3" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571756.6152567422</v>
+        <v>571757</v>
       </c>
       <c r="R3" t="n">
-        <v>6701619.375412359</v>
+        <v>6701620</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -903,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95887523</v>
+        <v>95887257</v>
       </c>
       <c r="B4" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571820.56332523</v>
+        <v>571814</v>
       </c>
       <c r="R4" t="n">
-        <v>6701486.369041326</v>
+        <v>6701526</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,12 +1005,7 @@
         <v>95887383</v>
       </c>
       <c r="B5" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571829.3233604587</v>
+        <v>571829</v>
       </c>
       <c r="R5" t="n">
-        <v>6701493.453908186</v>
+        <v>6701493</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1131,15 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95886455</v>
+        <v>95887523</v>
       </c>
       <c r="B6" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571761.1654026846</v>
+        <v>571820</v>
       </c>
       <c r="R6" t="n">
-        <v>6701589.353213356</v>
+        <v>6701486</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,59 +1220,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95886946</v>
+        <v>133625235</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Ovanskogen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571826.5494683493</v>
+        <v>571811</v>
       </c>
       <c r="R7" t="n">
-        <v>6701558.561436794</v>
+        <v>6701595</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,22 +1290,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,55 +1332,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95886767</v>
+        <v>131155670</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>SV om Skurtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571820.6340604525</v>
+        <v>571714</v>
       </c>
       <c r="R8" t="n">
-        <v>6701632.491079763</v>
+        <v>6701612</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,27 +1403,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>7 överblommade blomstänglar, hundratals bladrosetter över en area på cirka 50 kvm</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,64 +1423,68 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Tove Lawenius</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Fågelinventering Hålsberget 2024-2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95886868</v>
+        <v>95886895</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571829.3194432303</v>
+        <v>571836</v>
       </c>
       <c r="R9" t="n">
-        <v>6701568.489347048</v>
+        <v>6701558</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,12 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>9 överblommade blomstänglar, 100-tal bladrosetter</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,53 +1553,58 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133625235</v>
+        <v>95886579</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ovanskogen, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571811</v>
+        <v>571804</v>
       </c>
       <c r="R10" t="n">
-        <v>6701595</v>
+        <v>6701650</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1671,22 +1628,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133625236</v>
+        <v>95886767</v>
       </c>
       <c r="B11" t="n">
-        <v>99188</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,29 +1698,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ovanskogen, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571820</v>
+        <v>571821</v>
       </c>
       <c r="R11" t="n">
-        <v>6701600</v>
+        <v>6701632</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1787,22 +1737,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>7 överblommade blomstänglar, hundratals bladrosetter över en area på cirka 50 kvm</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,10 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133625237</v>
+        <v>95886822</v>
       </c>
       <c r="B12" t="n">
-        <v>99188</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,29 +1812,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ovanskogen, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571817</v>
+        <v>571808</v>
       </c>
       <c r="R12" t="n">
-        <v>6701631</v>
+        <v>6701595</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1903,22 +1851,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2021-09-03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3 överblommade blomstänglar, 100-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,6 +1895,465 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>95886868</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>571830</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6701568</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>9 överblommade blomstänglar, 100-tal bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>95886946</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>571826</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6701558</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133625236</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ovanskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>571820</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6701600</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133625237</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ovanskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>571817</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6701631</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45884-2021 artfynd.xlsx
+++ b/artfynd/A 45884-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95886455</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95886494</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95887257</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95887383</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95887523</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133625235</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131155670</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1550,6 +1590,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95886895</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95886579</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1781,6 +1831,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95886767</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1895,6 +1950,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95886822</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2009,6 +2069,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95886868</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2122,6 +2187,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95886946</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2238,6 +2308,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133625236</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2354,8 +2429,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133625237</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>